--- a/order_forms/016_custom_printing_order_form--order_forms.xlsx
+++ b/order_forms/016_custom_printing_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'a5'}</t>
+          <t>a5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'A5'}</t>
+          <t>A5</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'a6'}</t>
+          <t>a6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'A6'}</t>
+          <t>A6</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'a7'}</t>
+          <t>a7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'A7'}</t>
+          <t>A7</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'a8'}</t>
+          <t>a8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'A8'}</t>
+          <t>A8</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'a10'}</t>
+          <t>a10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'A10'}</t>
+          <t>A10</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'color'}</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Color'}</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'black_and_white'}</t>
+          <t>black_and_white</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Black and White'}</t>
+          <t>Black and White</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'glossy'}</t>
+          <t>glossy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Glossy'}</t>
+          <t>Glossy</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'matte'}</t>
+          <t>matte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Matte'}</t>
+          <t>Matte</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'matte_and_glossy'}</t>
+          <t>matte_and_glossy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Matte and Glossy'}</t>
+          <t>Matte and Glossy</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'cardstock'}</t>
+          <t>cardstock</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Cardstock'}</t>
+          <t>Cardstock</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'cotton'}</t>
+          <t>cotton</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Cotton'}</t>
+          <t>Cotton</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'vellum'}</t>
+          <t>vellum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Vellum'}</t>
+          <t>Vellum</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'8.5_x_11'}</t>
+          <t>8.5_x_11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '8.5 x 11'}</t>
+          <t>8.5 x 11</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'8.5_x_14'}</t>
+          <t>8.5_x_14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '8.5 x 14'}</t>
+          <t>8.5 x 14</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'letter'}</t>
+          <t>letter</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Letter'}</t>
+          <t>Letter</t>
         </is>
       </c>
     </row>
